--- a/Report/ProjectTracking - Group4.xlsx
+++ b/Report/ProjectTracking - Group4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Study\Ép pi ti\S5_SU26\SWP391\Sales Management Software\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E882971A-1E7F-4737-B6A6-59DA80A95A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA00A250-BE00-46C5-804C-C4B3C9813460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RMS" sheetId="1" r:id="rId1"/>
@@ -1492,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AB981"/>
@@ -1979,7 +1979,7 @@
       <c r="AA11" s="58"/>
       <c r="AB11" s="58"/>
     </row>
-    <row r="12" spans="1:28" s="50" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" s="50" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="50" t="s">
         <v>167</v>
       </c>
@@ -2019,7 +2019,7 @@
       <c r="AA12" s="55"/>
       <c r="AB12" s="55"/>
     </row>
-    <row r="13" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>167</v>
       </c>
@@ -2059,7 +2059,7 @@
       <c r="AA13" s="11"/>
       <c r="AB13" s="11"/>
     </row>
-    <row r="14" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>167</v>
       </c>
@@ -2099,7 +2099,7 @@
       <c r="AA14" s="11"/>
       <c r="AB14" s="11"/>
     </row>
-    <row r="15" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>167</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="AA15" s="11"/>
       <c r="AB15" s="11"/>
     </row>
-    <row r="16" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>167</v>
       </c>
@@ -2179,7 +2179,7 @@
       <c r="AA16" s="11"/>
       <c r="AB16" s="11"/>
     </row>
-    <row r="17" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>167</v>
       </c>
@@ -2219,7 +2219,7 @@
       <c r="AA17" s="11"/>
       <c r="AB17" s="11"/>
     </row>
-    <row r="18" spans="1:28" s="45" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" s="45" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="45" t="s">
         <v>167</v>
       </c>
@@ -2629,7 +2629,7 @@
       <c r="AA27" s="27"/>
       <c r="AB27" s="27"/>
     </row>
-    <row r="28" spans="1:28" s="50" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" s="50" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="50" t="s">
         <v>167</v>
       </c>
@@ -2669,7 +2669,7 @@
       <c r="AA28" s="55"/>
       <c r="AB28" s="55"/>
     </row>
-    <row r="29" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>167</v>
       </c>
@@ -2709,7 +2709,7 @@
       <c r="AA29" s="11"/>
       <c r="AB29" s="11"/>
     </row>
-    <row r="30" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>167</v>
       </c>
@@ -2749,7 +2749,7 @@
       <c r="AA30" s="11"/>
       <c r="AB30" s="11"/>
     </row>
-    <row r="31" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
         <v>167</v>
       </c>
@@ -2789,7 +2789,7 @@
       <c r="AA31" s="11"/>
       <c r="AB31" s="11"/>
     </row>
-    <row r="32" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>167</v>
       </c>
@@ -2829,7 +2829,7 @@
       <c r="AA32" s="11"/>
       <c r="AB32" s="11"/>
     </row>
-    <row r="33" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
         <v>167</v>
       </c>
@@ -2869,7 +2869,7 @@
       <c r="AA33" s="11"/>
       <c r="AB33" s="11"/>
     </row>
-    <row r="34" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
         <v>167</v>
       </c>
@@ -2909,7 +2909,7 @@
       <c r="AA34" s="11"/>
       <c r="AB34" s="11"/>
     </row>
-    <row r="35" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
         <v>167</v>
       </c>
@@ -2949,7 +2949,7 @@
       <c r="AA35" s="11"/>
       <c r="AB35" s="11"/>
     </row>
-    <row r="36" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
         <v>167</v>
       </c>
@@ -2989,7 +2989,7 @@
       <c r="AA36" s="11"/>
       <c r="AB36" s="11"/>
     </row>
-    <row r="37" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
         <v>167</v>
       </c>
@@ -3029,7 +3029,7 @@
       <c r="AA37" s="11"/>
       <c r="AB37" s="11"/>
     </row>
-    <row r="38" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
         <v>167</v>
       </c>
@@ -3069,7 +3069,7 @@
       <c r="AA38" s="11"/>
       <c r="AB38" s="11"/>
     </row>
-    <row r="39" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
         <v>167</v>
       </c>
@@ -3109,7 +3109,7 @@
       <c r="AA39" s="11"/>
       <c r="AB39" s="11"/>
     </row>
-    <row r="40" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>167</v>
       </c>
@@ -3149,7 +3149,7 @@
       <c r="AA40" s="11"/>
       <c r="AB40" s="11"/>
     </row>
-    <row r="41" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>167</v>
       </c>
@@ -3189,7 +3189,7 @@
       <c r="AA41" s="11"/>
       <c r="AB41" s="11"/>
     </row>
-    <row r="42" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>167</v>
       </c>
@@ -3229,7 +3229,7 @@
       <c r="AA42" s="11"/>
       <c r="AB42" s="11"/>
     </row>
-    <row r="43" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>167</v>
       </c>
@@ -3269,7 +3269,7 @@
       <c r="AA43" s="11"/>
       <c r="AB43" s="11"/>
     </row>
-    <row r="44" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>167</v>
       </c>
@@ -3309,7 +3309,7 @@
       <c r="AA44" s="11"/>
       <c r="AB44" s="11"/>
     </row>
-    <row r="45" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
         <v>167</v>
       </c>
@@ -3349,7 +3349,7 @@
       <c r="AA45" s="11"/>
       <c r="AB45" s="11"/>
     </row>
-    <row r="46" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
         <v>167</v>
       </c>
@@ -3387,7 +3387,7 @@
       <c r="AA46" s="11"/>
       <c r="AB46" s="11"/>
     </row>
-    <row r="47" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
         <v>167</v>
       </c>
@@ -3427,7 +3427,7 @@
       <c r="AA47" s="11"/>
       <c r="AB47" s="11"/>
     </row>
-    <row r="48" spans="1:28" s="45" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:28" s="45" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="45" t="s">
         <v>167</v>
       </c>
@@ -4293,7 +4293,7 @@
       <c r="AA68" s="27"/>
       <c r="AB68" s="27"/>
     </row>
-    <row r="69" spans="1:28" s="50" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:28" s="50" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="50" t="s">
         <v>167</v>
       </c>
@@ -4333,7 +4333,7 @@
       <c r="AA69" s="55"/>
       <c r="AB69" s="55"/>
     </row>
-    <row r="70" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="14" t="s">
         <v>167</v>
       </c>
@@ -4373,7 +4373,7 @@
       <c r="AA70" s="11"/>
       <c r="AB70" s="11"/>
     </row>
-    <row r="71" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="14" t="s">
         <v>167</v>
       </c>
@@ -4413,7 +4413,7 @@
       <c r="AA71" s="11"/>
       <c r="AB71" s="11"/>
     </row>
-    <row r="72" spans="1:28" s="45" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:28" s="45" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="45" t="s">
         <v>167</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="AA84" s="27"/>
       <c r="AB84" s="27"/>
     </row>
-    <row r="85" spans="1:28" s="50" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:28" s="50" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="50" t="s">
         <v>167</v>
       </c>
@@ -4977,7 +4977,7 @@
       <c r="AA85" s="55"/>
       <c r="AB85" s="55"/>
     </row>
-    <row r="86" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="14" t="s">
         <v>167</v>
       </c>
@@ -5017,7 +5017,7 @@
       <c r="AA86" s="11"/>
       <c r="AB86" s="11"/>
     </row>
-    <row r="87" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="14" t="s">
         <v>167</v>
       </c>
@@ -5057,7 +5057,7 @@
       <c r="AA87" s="11"/>
       <c r="AB87" s="11"/>
     </row>
-    <row r="88" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="14" t="s">
         <v>167</v>
       </c>
@@ -5097,7 +5097,7 @@
       <c r="AA88" s="11"/>
       <c r="AB88" s="11"/>
     </row>
-    <row r="89" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="14" t="s">
         <v>167</v>
       </c>
@@ -5137,7 +5137,7 @@
       <c r="AA89" s="11"/>
       <c r="AB89" s="11"/>
     </row>
-    <row r="90" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="14" t="s">
         <v>167</v>
       </c>
@@ -5177,7 +5177,7 @@
       <c r="AA90" s="11"/>
       <c r="AB90" s="11"/>
     </row>
-    <row r="91" spans="1:28" s="14" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:28" s="14" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="14" t="s">
         <v>167</v>
       </c>
@@ -5217,7 +5217,7 @@
       <c r="AA91" s="11"/>
       <c r="AB91" s="11"/>
     </row>
-    <row r="92" spans="1:28" s="45" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:28" s="45" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="45" t="s">
         <v>167</v>
       </c>
@@ -31293,11 +31293,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I984" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters blank="1">
-        <filter val="Function"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I983">
       <sortCondition descending="1" ref="E1:E984"/>
     </sortState>
@@ -31308,8 +31303,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -32866,6 +32861,7 @@
       <c r="H73" s="17" t="s">
         <v>10</v>
       </c>
+      <c r="I73" s="14"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="14" t="s">
@@ -32888,6 +32884,7 @@
       <c r="H74" s="17" t="s">
         <v>10</v>
       </c>
+      <c r="I74" s="14"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="14" t="s">
@@ -32910,6 +32907,7 @@
       <c r="H75" s="17" t="s">
         <v>10</v>
       </c>
+      <c r="I75" s="14"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="14" t="s">
@@ -32932,6 +32930,7 @@
       <c r="H76" s="17" t="s">
         <v>10</v>
       </c>
+      <c r="I76" s="14"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="14" t="s">
@@ -32954,6 +32953,7 @@
       <c r="H77" s="17" t="s">
         <v>10</v>
       </c>
+      <c r="I77" s="14"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -33886,8 +33886,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
